--- a/exports/trend_1d/APLAPOLLO_full_report.xlsx
+++ b/exports/trend_1d/APLAPOLLO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>16.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42159</v>
+        <v>42160</v>
       </c>
       <c r="H2" t="n">
-        <v>40.1</v>
+        <v>39.55</v>
       </c>
       <c r="I2" t="n">
         <v>39.86008242688374</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K2" t="n">
-        <v>9.710000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>8.07</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>12.76</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42198</v>
+        <v>42199</v>
       </c>
       <c r="H3" t="n">
-        <v>39.15</v>
+        <v>44.3</v>
       </c>
       <c r="I3" t="n">
         <v>42.5449599380552</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" t="n">
-        <v>1.01</v>
+        <v>-12.01</v>
       </c>
       <c r="L3" t="n">
-        <v>7.46</v>
+        <v>12.52</v>
       </c>
       <c r="M3" t="n">
         <v>2.34</v>
       </c>
       <c r="N3" t="n">
-        <v>7.4</v>
+        <v>13.15</v>
       </c>
       <c r="O3" t="n">
         <v>-1.37</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>18.04</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42387</v>
+        <v>42388</v>
       </c>
       <c r="H4" t="n">
-        <v>69.95</v>
+        <v>68.8</v>
       </c>
       <c r="I4" t="n">
         <v>69.01333094286265</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K4" t="n">
-        <v>57.9</v>
+        <v>55.3</v>
       </c>
       <c r="L4" t="n">
         <v>13.54</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>22.5</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42464</v>
+        <v>42465</v>
       </c>
       <c r="H5" t="n">
-        <v>68.55</v>
+        <v>69.75</v>
       </c>
       <c r="I5" t="n">
         <v>69.38605775457829</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K5" t="n">
-        <v>0.36</v>
+        <v>-1.38</v>
       </c>
       <c r="L5" t="n">
         <v>5.81</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.48</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42633</v>
+        <v>42634</v>
       </c>
       <c r="H6" t="n">
-        <v>92</v>
+        <v>89.2</v>
       </c>
       <c r="I6" t="n">
         <v>90.74574200349984</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K6" t="n">
-        <v>31.9</v>
+        <v>27.89</v>
       </c>
       <c r="L6" t="n">
         <v>1.79</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.32</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H7" t="n">
-        <v>95.09999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="I7" t="n">
         <v>95.73390339760201</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.61</v>
+        <v>-7.68</v>
       </c>
       <c r="L7" t="n">
-        <v>7.51</v>
+        <v>8.52</v>
       </c>
       <c r="M7" t="n">
         <v>2.96</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.52</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H8" t="n">
-        <v>139.15</v>
+        <v>133.2</v>
       </c>
       <c r="I8" t="n">
         <v>134.4344579720625</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K8" t="n">
-        <v>44.87</v>
+        <v>38.68</v>
       </c>
       <c r="L8" t="n">
         <v>0.9399999999999999</v>
@@ -897,7 +992,7 @@
         <v>1.96</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>4.28</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>14.87</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42893</v>
+        <v>42894</v>
       </c>
       <c r="H9" t="n">
-        <v>151.8</v>
+        <v>168.3</v>
       </c>
       <c r="I9" t="n">
         <v>153.0016240539261</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>-13.96</v>
+        <v>-26.35</v>
       </c>
       <c r="L9" t="n">
-        <v>14.11</v>
+        <v>27.55</v>
       </c>
       <c r="M9" t="n">
         <v>1.91</v>
       </c>
       <c r="N9" t="n">
-        <v>7.39</v>
+        <v>10.87</v>
       </c>
       <c r="O9" t="n">
         <v>-4.28</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>16.38</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42961</v>
+        <v>42963</v>
       </c>
       <c r="H10" t="n">
-        <v>152.6</v>
+        <v>149.65</v>
       </c>
       <c r="I10" t="n">
         <v>152.0495795181632</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.33</v>
+        <v>-11.08</v>
       </c>
       <c r="L10" t="n">
         <v>15</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.29</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42984</v>
+        <v>42985</v>
       </c>
       <c r="H11" t="n">
-        <v>160.5</v>
+        <v>161.35</v>
       </c>
       <c r="I11" t="n">
         <v>161.1396279771625</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.25</v>
+        <v>-7.82</v>
       </c>
       <c r="L11" t="n">
-        <v>7.58</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>1.87</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.88</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H12" t="n">
-        <v>225.5</v>
+        <v>214.35</v>
       </c>
       <c r="I12" t="n">
         <v>219.530104691136</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K12" t="n">
-        <v>39.76</v>
+        <v>32.85</v>
       </c>
       <c r="L12" t="n">
         <v>0.84</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>19.08</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H13" t="n">
-        <v>212.1</v>
+        <v>216.35</v>
       </c>
       <c r="I13" t="n">
         <v>213.2632501928647</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K13" t="n">
-        <v>1.05</v>
+        <v>-0.93</v>
       </c>
       <c r="L13" t="n">
         <v>5.44</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>10.9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H14" t="n">
-        <v>199.8</v>
+        <v>198.45</v>
       </c>
       <c r="I14" t="n">
         <v>199.7583564023076</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.65</v>
+        <v>-8.27</v>
       </c>
       <c r="L14" t="n">
-        <v>8.369999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>2.55</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.41</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43315</v>
+        <v>43318</v>
       </c>
       <c r="H15" t="n">
-        <v>169.9</v>
+        <v>180.15</v>
       </c>
       <c r="I15" t="n">
         <v>176.5779390742309</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K15" t="n">
-        <v>14.39</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -1296,7 +1475,7 @@
         <v>2.38</v>
       </c>
       <c r="N15" t="n">
-        <v>4.68</v>
+        <v>6.03</v>
       </c>
       <c r="O15" t="n">
         <v>-0.68</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>12.25</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H16" t="n">
-        <v>160.15</v>
+        <v>157.85</v>
       </c>
       <c r="I16" t="n">
         <v>158.0820992662223</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" t="n">
-        <v>-11.1</v>
+        <v>-12.38</v>
       </c>
       <c r="L16" t="n">
-        <v>12.27</v>
+        <v>16.18</v>
       </c>
       <c r="M16" t="n">
         <v>1.75</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.05</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43523</v>
+        <v>43524</v>
       </c>
       <c r="H17" t="n">
-        <v>115.6</v>
+        <v>119.9</v>
       </c>
       <c r="I17" t="n">
         <v>118.3622823711</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K17" t="n">
-        <v>26.77</v>
+        <v>24.04</v>
       </c>
       <c r="L17" t="n">
         <v>2.28</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>14.45</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H18" t="n">
-        <v>152.2</v>
+        <v>149.95</v>
       </c>
       <c r="I18" t="n">
         <v>152.1499700885547</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K18" t="n">
-        <v>26.94</v>
+        <v>25.06</v>
       </c>
       <c r="L18" t="n">
         <v>3.84</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.5</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H19" t="n">
-        <v>130.9</v>
+        <v>140.6</v>
       </c>
       <c r="I19" t="n">
         <v>139.8759774742383</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K19" t="n">
-        <v>12.7</v>
+        <v>6.24</v>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>4.7</v>
       </c>
       <c r="M19" t="n">
         <v>3.23</v>
       </c>
       <c r="N19" t="n">
-        <v>4.83</v>
+        <v>7.41</v>
       </c>
       <c r="O19" t="n">
         <v>-1.48</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.51</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43862</v>
+        <v>43864</v>
       </c>
       <c r="H20" t="n">
-        <v>197.2</v>
+        <v>192.15</v>
       </c>
       <c r="I20" t="n">
         <v>193.4148496665651</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K20" t="n">
-        <v>40.26</v>
+        <v>36.66</v>
       </c>
       <c r="L20" t="n">
         <v>7.54</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="H21" t="n">
-        <v>141.25</v>
+        <v>151.75</v>
       </c>
       <c r="I21" t="n">
         <v>145.2839589294338</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K21" t="n">
-        <v>26.49</v>
+        <v>21.03</v>
       </c>
       <c r="L21" t="n">
         <v>12.7</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>17.5</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44267</v>
+        <v>44270</v>
       </c>
       <c r="H22" t="n">
-        <v>628.75</v>
+        <v>572.25</v>
       </c>
       <c r="I22" t="n">
         <v>595.4170043038214</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K22" t="n">
-        <v>314.33</v>
+        <v>277.1</v>
       </c>
       <c r="L22" t="n">
         <v>6.92</v>
@@ -1695,7 +1958,7 @@
         <v>4.29</v>
       </c>
       <c r="N22" t="n">
-        <v>5.84</v>
+        <v>8.99</v>
       </c>
       <c r="O22" t="n">
         <v>7.43</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>201</v>
+        <v>202</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>10</v>
+      </c>
+      <c r="U22" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>22.58</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44277</v>
+        <v>44278</v>
       </c>
       <c r="H23" t="n">
-        <v>641.9</v>
+        <v>660.85</v>
       </c>
       <c r="I23" t="n">
         <v>657.5623053786366</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-12.17</v>
+        <v>-15.48</v>
       </c>
       <c r="L23" t="n">
-        <v>13.32</v>
+        <v>17.61</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>18.03</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44302</v>
+        <v>44305</v>
       </c>
       <c r="H24" t="n">
-        <v>629.2</v>
+        <v>592.5</v>
       </c>
       <c r="I24" t="n">
         <v>594.9656286760196</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.79</v>
+        <v>-10.34</v>
       </c>
       <c r="L24" t="n">
-        <v>10.23</v>
+        <v>11.48</v>
       </c>
       <c r="M24" t="n">
-        <v>0.92</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
         <v>6.87</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>19.42</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44356</v>
+        <v>44357</v>
       </c>
       <c r="H25" t="n">
-        <v>684.5</v>
+        <v>712.75</v>
       </c>
       <c r="I25" t="n">
         <v>698.3682525867345</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K25" t="n">
-        <v>-15.53</v>
+        <v>-20.3</v>
       </c>
       <c r="L25" t="n">
-        <v>19.66</v>
+        <v>23.04</v>
       </c>
       <c r="M25" t="n">
         <v>2.79</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.84</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44390</v>
+        <v>44391</v>
       </c>
       <c r="H26" t="n">
-        <v>745.35</v>
+        <v>723.8</v>
       </c>
       <c r="I26" t="n">
         <v>733.9675526184491</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>4.57</v>
+        <v>1.55</v>
       </c>
       <c r="L26" t="n">
         <v>3.71</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>13.38</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H27" t="n">
-        <v>804.8</v>
+        <v>875.3</v>
       </c>
       <c r="I27" t="n">
         <v>820.6770456906272</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-11.19</v>
+        <v>-20.93</v>
       </c>
       <c r="L27" t="n">
-        <v>15.02</v>
+        <v>25.99</v>
       </c>
       <c r="M27" t="n">
         <v>1.8</v>
       </c>
       <c r="N27" t="n">
-        <v>5.09</v>
+        <v>8.76</v>
       </c>
       <c r="O27" t="n">
         <v>-2.89</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>16</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H28" t="n">
-        <v>803.05</v>
+        <v>771.7</v>
       </c>
       <c r="I28" t="n">
         <v>786.2163552555785</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.25</v>
+        <v>-11.84</v>
       </c>
       <c r="L28" t="n">
-        <v>9.75</v>
+        <v>13.17</v>
       </c>
       <c r="M28" t="n">
         <v>0.66</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>16.37</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44445</v>
+        <v>44446</v>
       </c>
       <c r="H29" t="n">
-        <v>851.5</v>
+        <v>882.45</v>
       </c>
       <c r="I29" t="n">
         <v>865.0276942680995</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>-10.34</v>
+        <v>-14.35</v>
       </c>
       <c r="L29" t="n">
-        <v>11.12</v>
+        <v>15</v>
       </c>
       <c r="M29" t="n">
         <v>1.99</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.84</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44466</v>
+        <v>44467</v>
       </c>
       <c r="H30" t="n">
-        <v>868.85</v>
+        <v>847.85</v>
       </c>
       <c r="I30" t="n">
         <v>862.5028950925139</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.54</v>
+        <v>-3.92</v>
       </c>
       <c r="L30" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="M30" t="n">
         <v>0.52</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>15.71</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="H31" t="n">
-        <v>883.7</v>
+        <v>908.7</v>
       </c>
       <c r="I31" t="n">
         <v>900.9914167525751</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.23</v>
+        <v>-7.18</v>
       </c>
       <c r="L31" t="n">
-        <v>5.56</v>
+        <v>8.5</v>
       </c>
       <c r="M31" t="n">
         <v>2.13</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.43</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H32" t="n">
-        <v>949.15</v>
+        <v>948.2</v>
       </c>
       <c r="I32" t="n">
         <v>949.0383017370165</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K32" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="L32" t="n">
         <v>9.470000000000001</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>14.49</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44634</v>
+        <v>44635</v>
       </c>
       <c r="H33" t="n">
-        <v>886.3</v>
+        <v>918.65</v>
       </c>
       <c r="I33" t="n">
         <v>911.5805129810219</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K33" t="n">
-        <v>6.53</v>
+        <v>3.12</v>
       </c>
       <c r="L33" t="n">
         <v>4.23</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>14.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H34" t="n">
-        <v>949.95</v>
+        <v>893.75</v>
       </c>
       <c r="I34" t="n">
         <v>938.7800097276697</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K34" t="n">
-        <v>3.41</v>
+        <v>-2.71</v>
       </c>
       <c r="L34" t="n">
-        <v>4.03</v>
+        <v>6.93</v>
       </c>
       <c r="M34" t="n">
         <v>3.78</v>
       </c>
       <c r="N34" t="n">
-        <v>5.29</v>
+        <v>5.92</v>
       </c>
       <c r="O34" t="n">
         <v>3.65</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>16.78</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44713</v>
+        <v>44714</v>
       </c>
       <c r="H35" t="n">
-        <v>985.3</v>
+        <v>994.3</v>
       </c>
       <c r="I35" t="n">
         <v>986.7041297910433</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.24</v>
+        <v>-11.25</v>
       </c>
       <c r="L35" t="n">
-        <v>10.77</v>
+        <v>11.89</v>
       </c>
       <c r="M35" t="n">
         <v>2.99</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>14.72</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44728</v>
+        <v>44729</v>
       </c>
       <c r="H36" t="n">
-        <v>892.45</v>
+        <v>857.1</v>
       </c>
       <c r="I36" t="n">
         <v>868.0393084663732</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K36" t="n">
-        <v>-10.24</v>
+        <v>-13.8</v>
       </c>
       <c r="L36" t="n">
-        <v>12.58</v>
+        <v>14.31</v>
       </c>
       <c r="M36" t="n">
         <v>2.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="O36" t="n">
         <v>0.91</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>17.07</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H37" t="n">
-        <v>922.7</v>
+        <v>955.75</v>
       </c>
       <c r="I37" t="n">
         <v>953.9150660129944</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.65</v>
+        <v>-11.51</v>
       </c>
       <c r="L37" t="n">
-        <v>9.460000000000001</v>
+        <v>12.79</v>
       </c>
       <c r="M37" t="n">
         <v>1.3</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.57</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44798</v>
+        <v>44799</v>
       </c>
       <c r="H38" t="n">
-        <v>1025.25</v>
+        <v>976.15</v>
       </c>
       <c r="I38" t="n">
         <v>982.9739374668138</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K38" t="n">
-        <v>7.27</v>
+        <v>2.13</v>
       </c>
       <c r="L38" t="n">
         <v>2.7</v>
@@ -2607,7 +3062,7 @@
         <v>0.71</v>
       </c>
       <c r="N38" t="n">
-        <v>2.97</v>
+        <v>4.79</v>
       </c>
       <c r="O38" t="n">
         <v>3.58</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>18.1</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H39" t="n">
-        <v>1097.4</v>
+        <v>1137.3</v>
       </c>
       <c r="I39" t="n">
         <v>1102.660068581379</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.42</v>
+        <v>-16.51</v>
       </c>
       <c r="L39" t="n">
-        <v>14.02</v>
+        <v>20.58</v>
       </c>
       <c r="M39" t="n">
         <v>4.62</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>11.87</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H40" t="n">
-        <v>1108.95</v>
+        <v>1061.75</v>
       </c>
       <c r="I40" t="n">
         <v>1062.134023150094</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.49</v>
+        <v>-6.64</v>
       </c>
       <c r="L40" t="n">
         <v>13.13</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>3.65</v>
+        <v>4.26</v>
       </c>
       <c r="O40" t="n">
         <v>3.64</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>13.31</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44943</v>
+        <v>44944</v>
       </c>
       <c r="H41" t="n">
-        <v>1142.2</v>
+        <v>1188.9</v>
       </c>
       <c r="I41" t="n">
         <v>1164.662741853091</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.58</v>
+        <v>-11.98</v>
       </c>
       <c r="L41" t="n">
-        <v>8.31</v>
+        <v>12.08</v>
       </c>
       <c r="M41" t="n">
         <v>0.77</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.52</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45058</v>
+        <v>45061</v>
       </c>
       <c r="H42" t="n">
-        <v>1179.75</v>
+        <v>1152.05</v>
       </c>
       <c r="I42" t="n">
         <v>1177.707196543892</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.77</v>
+        <v>-3.1</v>
       </c>
       <c r="L42" t="n">
         <v>6.64</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.02</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45084</v>
+        <v>45085</v>
       </c>
       <c r="H43" t="n">
-        <v>1177.95</v>
+        <v>1201.25</v>
       </c>
       <c r="I43" t="n">
         <v>1180.249831927972</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.25</v>
+        <v>-4.27</v>
       </c>
       <c r="L43" t="n">
-        <v>3.45</v>
+        <v>5.13</v>
       </c>
       <c r="M43" t="n">
         <v>1.45</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.59</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45190</v>
+        <v>45191</v>
       </c>
       <c r="H44" t="n">
-        <v>1600.5</v>
+        <v>1578.25</v>
       </c>
       <c r="I44" t="n">
         <v>1593.154780527159</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K44" t="n">
-        <v>33.24</v>
+        <v>31.38</v>
       </c>
       <c r="L44" t="n">
         <v>2.06</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>10.82</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45211</v>
+        <v>45212</v>
       </c>
       <c r="H45" t="n">
-        <v>1676.05</v>
+        <v>1712.15</v>
       </c>
       <c r="I45" t="n">
         <v>1692.571736480031</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.2</v>
+        <v>-8.48</v>
       </c>
       <c r="L45" t="n">
-        <v>7.06</v>
+        <v>9.17</v>
       </c>
       <c r="M45" t="n">
         <v>0.8100000000000001</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>10.43</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H46" t="n">
-        <v>1624.55</v>
+        <v>1596.95</v>
       </c>
       <c r="I46" t="n">
         <v>1597.82330070672</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.12</v>
+        <v>-6.73</v>
       </c>
       <c r="L46" t="n">
-        <v>6.41</v>
+        <v>7.28</v>
       </c>
       <c r="M46" t="n">
         <v>1.1</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.26</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="H47" t="n">
-        <v>1462.8</v>
+        <v>1547.55</v>
       </c>
       <c r="I47" t="n">
         <v>1476.95284482528</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K47" t="n">
-        <v>8.4</v>
+        <v>3.09</v>
       </c>
       <c r="L47" t="n">
         <v>11.09</v>
@@ -3120,7 +3683,7 @@
         <v>2.92</v>
       </c>
       <c r="N47" t="n">
-        <v>5.02</v>
+        <v>5.79</v>
       </c>
       <c r="O47" t="n">
         <v>-1.7</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.69</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H48" t="n">
-        <v>1598.25</v>
+        <v>1533.25</v>
       </c>
       <c r="I48" t="n">
         <v>1553.721836749944</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K48" t="n">
-        <v>3.28</v>
+        <v>-0.92</v>
       </c>
       <c r="L48" t="n">
         <v>7.01</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.96</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45531</v>
+        <v>45532</v>
       </c>
       <c r="H49" t="n">
-        <v>1441.9</v>
+        <v>1475.6</v>
       </c>
       <c r="I49" t="n">
         <v>1471.981385729447</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K49" t="n">
-        <v>5.96</v>
+        <v>3.76</v>
       </c>
       <c r="L49" t="n">
         <v>9.51</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.85</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H50" t="n">
-        <v>1491.85</v>
+        <v>1473.7</v>
       </c>
       <c r="I50" t="n">
         <v>1475.313677386433</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K50" t="n">
-        <v>1.1</v>
+        <v>-0.13</v>
       </c>
       <c r="L50" t="n">
         <v>6.31</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.2</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H51" t="n">
-        <v>1556.8</v>
+        <v>1580.55</v>
       </c>
       <c r="I51" t="n">
         <v>1579.640303748699</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.64</v>
+        <v>-7.25</v>
       </c>
       <c r="L51" t="n">
-        <v>6.3</v>
+        <v>7.61</v>
       </c>
       <c r="M51" t="n">
         <v>2.24</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>10.26</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H52" t="n">
-        <v>1520.7</v>
+        <v>1424.1</v>
       </c>
       <c r="I52" t="n">
         <v>1483.706379653884</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.79</v>
+        <v>-9.9</v>
       </c>
       <c r="L52" t="n">
-        <v>6.8</v>
+        <v>10.45</v>
       </c>
       <c r="M52" t="n">
         <v>1.66</v>
       </c>
       <c r="N52" t="n">
-        <v>3.42</v>
+        <v>6.35</v>
       </c>
       <c r="O52" t="n">
         <v>1.53</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.94</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45708</v>
+        <v>45709</v>
       </c>
       <c r="H53" t="n">
-        <v>1476.6</v>
+        <v>1489.2</v>
       </c>
       <c r="I53" t="n">
         <v>1488.684363898474</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.69</v>
+        <v>-4.57</v>
       </c>
       <c r="L53" t="n">
         <v>15.4</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.93</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H54" t="n">
-        <v>1798.8</v>
+        <v>1771.9</v>
       </c>
       <c r="I54" t="n">
         <v>1795.032010764836</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K54" t="n">
-        <v>20.79</v>
+        <v>18.98</v>
       </c>
       <c r="L54" t="n">
         <v>8.34</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.89</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="H55" t="n">
-        <v>1653.7</v>
+        <v>1674.8</v>
       </c>
       <c r="I55" t="n">
         <v>1657.552588225145</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K55" t="n">
-        <v>6.67</v>
+        <v>5.48</v>
       </c>
       <c r="L55" t="n">
         <v>3.33</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>7.76</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H56" t="n">
-        <v>2152.8</v>
+        <v>2097.9</v>
       </c>
       <c r="I56" t="n">
         <v>2116.757492747131</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K56" t="n">
-        <v>28.54</v>
+        <v>25.26</v>
       </c>
       <c r="L56" t="n">
         <v>1.77</v>
       </c>
       <c r="M56" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="N56" t="n">
         <v>4.62</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>7</v>
+      </c>
+      <c r="U56" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.4</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="H57" t="n">
-        <v>2105.7</v>
+        <v>2143.9</v>
       </c>
       <c r="I57" t="n">
         <v>2108.539525977659</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.37</v>
+        <v>-2.19</v>
       </c>
       <c r="L57" t="n">
         <v>3.37</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>11.51</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H58" t="n">
-        <v>1966.6</v>
+        <v>1905</v>
       </c>
       <c r="I58" t="n">
         <v>1908.995036777057</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.27</v>
+        <v>-11.14</v>
       </c>
       <c r="L58" t="n">
-        <v>8.67</v>
+        <v>11.59</v>
       </c>
       <c r="M58" t="n">
-        <v>0.04</v>
+        <v>0.51</v>
       </c>
       <c r="N58" t="n">
         <v>4.67</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.76</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H59" t="n">
-        <v>1819.5</v>
+        <v>1941.5</v>
       </c>
       <c r="I59" t="n">
         <v>1894.77597232093</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K59" t="n">
-        <v>4.49</v>
+        <v>-1.92</v>
       </c>
       <c r="L59" t="n">
         <v>5.6</v>
@@ -3804,7 +4511,7 @@
         <v>1.62</v>
       </c>
       <c r="N59" t="n">
-        <v>3.08</v>
+        <v>6.71</v>
       </c>
       <c r="O59" t="n">
         <v>-3.13</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.62</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H60" t="n">
-        <v>2135</v>
+        <v>2040</v>
       </c>
       <c r="I60" t="n">
         <v>2081.818906776944</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K60" t="n">
-        <v>9.970000000000001</v>
+        <v>5.07</v>
       </c>
       <c r="L60" t="n">
         <v>6.24</v>
@@ -3861,7 +4580,7 @@
         <v>2.02</v>
       </c>
       <c r="N60" t="n">
-        <v>3.92</v>
+        <v>4.45</v>
       </c>
       <c r="O60" t="n">
         <v>6.71</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>11.66</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H61" t="n">
-        <v>2077.9</v>
+        <v>2213.9</v>
       </c>
       <c r="I61" t="n">
         <v>2209.231375508443</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.86</v>
+        <v>-8.52</v>
       </c>
       <c r="L61" t="n">
-        <v>7.29</v>
+        <v>8.52</v>
       </c>
       <c r="M61" t="n">
-        <v>0.6</v>
+        <v>1.26</v>
       </c>
       <c r="N61" t="n">
-        <v>3.63</v>
+        <v>6.55</v>
       </c>
       <c r="O61" t="n">
         <v>-4.45</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,12 @@
       <c r="Q62" t="n">
         <v>2</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8936,7 +9685,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.3</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="6">
@@ -8946,7 +9695,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -8956,7 +9705,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
@@ -8966,7 +9715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -8976,7 +9725,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106.5</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="10">
@@ -8986,7 +9735,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140.5</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="11">
@@ -9026,7 +9775,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.74</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="15">
@@ -9036,7 +9785,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20.3</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="16">
@@ -9046,7 +9795,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="17">
@@ -9056,7 +9805,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>314.33</v>
+        <v>277.1</v>
       </c>
     </row>
     <row r="18">
@@ -9066,7 +9815,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="19">
@@ -9076,7 +9825,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.63</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9086,7 +9835,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.18</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="21">
@@ -9096,7 +9845,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.66</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="22">
@@ -9106,7 +9855,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9116,7 +9865,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -9126,7 +9875,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="25">
@@ -9146,7 +9895,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.15</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="27">
@@ -9166,7 +9915,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
